--- a/artfynd/A 60580-2024 artfynd.xlsx
+++ b/artfynd/A 60580-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122386318</v>
+        <v>122386320</v>
       </c>
       <c r="B2" t="n">
         <v>57374</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>482996</v>
+        <v>482875</v>
       </c>
       <c r="R2" t="n">
-        <v>6989426</v>
+        <v>6989223</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -755,7 +755,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -785,7 +785,7 @@
         <v>122386324</v>
       </c>
       <c r="B3" t="n">
-        <v>79726</v>
+        <v>79727</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -884,7 +884,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122386315</v>
+        <v>122386322</v>
       </c>
       <c r="B4" t="n">
         <v>57374</v>
@@ -917,33 +917,17 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Låshålet, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>483057</v>
+        <v>482807</v>
       </c>
       <c r="R4" t="n">
-        <v>6989286</v>
+        <v>6989125</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -976,6 +960,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-01-30</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>ringhack färska</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1002,10 +991,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122386319</v>
+        <v>122386323</v>
       </c>
       <c r="B5" t="n">
-        <v>57374</v>
+        <v>57390</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1018,16 +1007,16 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1042,10 +1031,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>482918</v>
+        <v>483129</v>
       </c>
       <c r="R5" t="n">
-        <v>6989264</v>
+        <v>6989526</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1082,7 +1071,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>hack</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1109,7 +1098,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122386321</v>
+        <v>122386318</v>
       </c>
       <c r="B6" t="n">
         <v>57374</v>
@@ -1149,10 +1138,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>482832</v>
+        <v>482996</v>
       </c>
       <c r="R6" t="n">
-        <v>6989152</v>
+        <v>6989426</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1189,7 +1178,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>ringhack färska</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1216,7 +1205,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122386313</v>
+        <v>122386321</v>
       </c>
       <c r="B7" t="n">
         <v>57374</v>
@@ -1256,10 +1245,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>483001</v>
+        <v>482832</v>
       </c>
       <c r="R7" t="n">
-        <v>6989219</v>
+        <v>6989152</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1296,7 +1285,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>ringhack</t>
+          <t>ringhack färska</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1323,7 +1312,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122386317</v>
+        <v>122386315</v>
       </c>
       <c r="B8" t="n">
         <v>57374</v>
@@ -1356,17 +1345,33 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr"/>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Låshålet, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>483013</v>
+        <v>483057</v>
       </c>
       <c r="R8" t="n">
-        <v>6989410</v>
+        <v>6989286</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1399,11 +1404,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-01-30</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1430,7 +1430,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122386311</v>
+        <v>122386310</v>
       </c>
       <c r="B9" t="n">
         <v>57374</v>
@@ -1470,10 +1470,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>483013</v>
+        <v>483003</v>
       </c>
       <c r="R9" t="n">
-        <v>6989190</v>
+        <v>6989199</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1537,7 +1537,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122386310</v>
+        <v>122386311</v>
       </c>
       <c r="B10" t="n">
         <v>57374</v>
@@ -1577,10 +1577,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>483003</v>
+        <v>483013</v>
       </c>
       <c r="R10" t="n">
-        <v>6989199</v>
+        <v>6989190</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1644,7 +1644,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122386320</v>
+        <v>122386317</v>
       </c>
       <c r="B11" t="n">
         <v>57374</v>
@@ -1684,10 +1684,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>482875</v>
+        <v>483013</v>
       </c>
       <c r="R11" t="n">
-        <v>6989223</v>
+        <v>6989410</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1724,7 +1724,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1751,10 +1751,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122386323</v>
+        <v>122386314</v>
       </c>
       <c r="B12" t="n">
-        <v>57390</v>
+        <v>57374</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1767,16 +1767,16 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1785,16 +1785,28 @@
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Låshålet, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>483129</v>
+        <v>482998</v>
       </c>
       <c r="R12" t="n">
-        <v>6989526</v>
+        <v>6989231</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1827,11 +1839,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-01-30</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>hack</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1858,7 +1865,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122386322</v>
+        <v>122386316</v>
       </c>
       <c r="B13" t="n">
         <v>57374</v>
@@ -1898,10 +1905,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>482807</v>
+        <v>483242</v>
       </c>
       <c r="R13" t="n">
-        <v>6989125</v>
+        <v>6989315</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1938,7 +1945,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>ringhack färska</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1965,10 +1972,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122386328</v>
+        <v>122386313</v>
       </c>
       <c r="B14" t="n">
-        <v>90797</v>
+        <v>57374</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1981,21 +1988,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2005,10 +2012,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>483144</v>
+        <v>483001</v>
       </c>
       <c r="R14" t="n">
-        <v>6989488</v>
+        <v>6989219</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2041,6 +2048,11 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-01-30</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2067,7 +2079,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122386314</v>
+        <v>122386319</v>
       </c>
       <c r="B15" t="n">
         <v>57374</v>
@@ -2101,28 +2113,16 @@
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Låshålet, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>482998</v>
+        <v>482918</v>
       </c>
       <c r="R15" t="n">
-        <v>6989231</v>
+        <v>6989264</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2155,6 +2155,11 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-01-30</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2181,10 +2186,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122386316</v>
+        <v>122386328</v>
       </c>
       <c r="B16" t="n">
-        <v>57374</v>
+        <v>90807</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2197,21 +2202,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2221,10 +2226,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>483242</v>
+        <v>483144</v>
       </c>
       <c r="R16" t="n">
-        <v>6989315</v>
+        <v>6989488</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2257,11 +2262,6 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-01-30</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD16" t="b">

--- a/artfynd/A 60580-2024 artfynd.xlsx
+++ b/artfynd/A 60580-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122386320</v>
+        <v>122386319</v>
       </c>
       <c r="B2" t="n">
         <v>57374</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>482875</v>
+        <v>482918</v>
       </c>
       <c r="R2" t="n">
-        <v>6989223</v>
+        <v>6989264</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -755,7 +755,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122386324</v>
+        <v>122386313</v>
       </c>
       <c r="B3" t="n">
-        <v>79727</v>
+        <v>57374</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,21 +798,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>483051</v>
+        <v>483001</v>
       </c>
       <c r="R3" t="n">
-        <v>6989494</v>
+        <v>6989219</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -858,6 +858,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-01-30</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -884,7 +889,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122386322</v>
+        <v>122386316</v>
       </c>
       <c r="B4" t="n">
         <v>57374</v>
@@ -924,10 +929,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>482807</v>
+        <v>483242</v>
       </c>
       <c r="R4" t="n">
-        <v>6989125</v>
+        <v>6989315</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -964,7 +969,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>ringhack färska</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -991,10 +996,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122386323</v>
+        <v>122386322</v>
       </c>
       <c r="B5" t="n">
-        <v>57390</v>
+        <v>57374</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1007,16 +1012,16 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1031,10 +1036,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>483129</v>
+        <v>482807</v>
       </c>
       <c r="R5" t="n">
-        <v>6989526</v>
+        <v>6989125</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1071,7 +1076,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>hack</t>
+          <t>ringhack färska</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1205,10 +1210,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122386321</v>
+        <v>122386324</v>
       </c>
       <c r="B7" t="n">
-        <v>57374</v>
+        <v>79727</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1221,21 +1226,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1245,10 +1250,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>482832</v>
+        <v>483051</v>
       </c>
       <c r="R7" t="n">
-        <v>6989152</v>
+        <v>6989494</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1281,11 +1286,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-01-30</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>ringhack färska</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1312,10 +1312,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122386315</v>
+        <v>122386323</v>
       </c>
       <c r="B8" t="n">
-        <v>57374</v>
+        <v>57390</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1328,16 +1328,16 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1345,33 +1345,17 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Låshålet, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>483057</v>
+        <v>483129</v>
       </c>
       <c r="R8" t="n">
-        <v>6989286</v>
+        <v>6989526</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1404,6 +1388,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-01-30</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>hack</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1430,7 +1419,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122386310</v>
+        <v>122386317</v>
       </c>
       <c r="B9" t="n">
         <v>57374</v>
@@ -1470,10 +1459,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>483003</v>
+        <v>483013</v>
       </c>
       <c r="R9" t="n">
-        <v>6989199</v>
+        <v>6989410</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1537,7 +1526,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122386311</v>
+        <v>122386310</v>
       </c>
       <c r="B10" t="n">
         <v>57374</v>
@@ -1577,10 +1566,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>483013</v>
+        <v>483003</v>
       </c>
       <c r="R10" t="n">
-        <v>6989190</v>
+        <v>6989199</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1644,10 +1633,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122386317</v>
+        <v>122386328</v>
       </c>
       <c r="B11" t="n">
-        <v>57374</v>
+        <v>90807</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1660,21 +1649,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1684,10 +1673,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>483013</v>
+        <v>483144</v>
       </c>
       <c r="R11" t="n">
-        <v>6989410</v>
+        <v>6989488</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1720,11 +1709,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-01-30</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1865,7 +1849,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122386316</v>
+        <v>122386321</v>
       </c>
       <c r="B13" t="n">
         <v>57374</v>
@@ -1905,10 +1889,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>483242</v>
+        <v>482832</v>
       </c>
       <c r="R13" t="n">
-        <v>6989315</v>
+        <v>6989152</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1945,7 +1929,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1972,7 +1956,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122386313</v>
+        <v>122386320</v>
       </c>
       <c r="B14" t="n">
         <v>57374</v>
@@ -2012,10 +1996,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>483001</v>
+        <v>482875</v>
       </c>
       <c r="R14" t="n">
-        <v>6989219</v>
+        <v>6989223</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2052,7 +2036,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>ringhack</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2079,7 +2063,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122386319</v>
+        <v>122386315</v>
       </c>
       <c r="B15" t="n">
         <v>57374</v>
@@ -2112,17 +2096,33 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr"/>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Låshålet, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>482918</v>
+        <v>483057</v>
       </c>
       <c r="R15" t="n">
-        <v>6989264</v>
+        <v>6989286</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2155,11 +2155,6 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-01-30</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2186,10 +2181,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122386328</v>
+        <v>122386311</v>
       </c>
       <c r="B16" t="n">
-        <v>90807</v>
+        <v>57374</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2202,21 +2197,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2226,10 +2221,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>483144</v>
+        <v>483013</v>
       </c>
       <c r="R16" t="n">
-        <v>6989488</v>
+        <v>6989190</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2262,6 +2257,11 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-01-30</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD16" t="b">

--- a/artfynd/A 60580-2024 artfynd.xlsx
+++ b/artfynd/A 60580-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122386319</v>
+        <v>122386317</v>
       </c>
       <c r="B2" t="n">
-        <v>57374</v>
+        <v>57379</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>482918</v>
+        <v>483013</v>
       </c>
       <c r="R2" t="n">
-        <v>6989264</v>
+        <v>6989410</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122386313</v>
+        <v>122386322</v>
       </c>
       <c r="B3" t="n">
-        <v>57374</v>
+        <v>57379</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>483001</v>
+        <v>482807</v>
       </c>
       <c r="R3" t="n">
-        <v>6989219</v>
+        <v>6989125</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -862,7 +862,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>ringhack</t>
+          <t>ringhack färska</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -892,7 +892,7 @@
         <v>122386316</v>
       </c>
       <c r="B4" t="n">
-        <v>57374</v>
+        <v>57379</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -996,10 +996,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122386322</v>
+        <v>122386315</v>
       </c>
       <c r="B5" t="n">
-        <v>57374</v>
+        <v>57379</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1029,17 +1029,33 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr"/>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Låshålet, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>482807</v>
+        <v>483057</v>
       </c>
       <c r="R5" t="n">
-        <v>6989125</v>
+        <v>6989286</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1072,11 +1088,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-01-30</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>ringhack färska</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1106,7 +1117,7 @@
         <v>122386318</v>
       </c>
       <c r="B6" t="n">
-        <v>57374</v>
+        <v>57379</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1213,7 +1224,7 @@
         <v>122386324</v>
       </c>
       <c r="B7" t="n">
-        <v>79727</v>
+        <v>79732</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1315,7 +1326,7 @@
         <v>122386323</v>
       </c>
       <c r="B8" t="n">
-        <v>57390</v>
+        <v>57395</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1419,10 +1430,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122386317</v>
+        <v>122386320</v>
       </c>
       <c r="B9" t="n">
-        <v>57374</v>
+        <v>57379</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1459,10 +1470,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>483013</v>
+        <v>482875</v>
       </c>
       <c r="R9" t="n">
-        <v>6989410</v>
+        <v>6989223</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1499,7 +1510,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1526,10 +1537,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122386310</v>
+        <v>122386321</v>
       </c>
       <c r="B10" t="n">
-        <v>57374</v>
+        <v>57379</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1566,10 +1577,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>483003</v>
+        <v>482832</v>
       </c>
       <c r="R10" t="n">
-        <v>6989199</v>
+        <v>6989152</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1606,7 +1617,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1633,10 +1644,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122386328</v>
+        <v>122386310</v>
       </c>
       <c r="B11" t="n">
-        <v>90807</v>
+        <v>57379</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1649,21 +1660,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1673,10 +1684,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>483144</v>
+        <v>483003</v>
       </c>
       <c r="R11" t="n">
-        <v>6989488</v>
+        <v>6989199</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1709,6 +1720,11 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-01-30</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1735,10 +1751,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122386314</v>
+        <v>122386313</v>
       </c>
       <c r="B12" t="n">
-        <v>57374</v>
+        <v>57379</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1769,28 +1785,16 @@
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Låshålet, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>482998</v>
+        <v>483001</v>
       </c>
       <c r="R12" t="n">
-        <v>6989231</v>
+        <v>6989219</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1823,6 +1827,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-01-30</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1849,10 +1858,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122386321</v>
+        <v>122386319</v>
       </c>
       <c r="B13" t="n">
-        <v>57374</v>
+        <v>57379</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1889,10 +1898,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>482832</v>
+        <v>482918</v>
       </c>
       <c r="R13" t="n">
-        <v>6989152</v>
+        <v>6989264</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1929,7 +1938,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>ringhack färska</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1956,10 +1965,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122386320</v>
+        <v>122386311</v>
       </c>
       <c r="B14" t="n">
-        <v>57374</v>
+        <v>57379</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1996,10 +2005,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>482875</v>
+        <v>483013</v>
       </c>
       <c r="R14" t="n">
-        <v>6989223</v>
+        <v>6989190</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2036,7 +2045,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2063,10 +2072,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122386315</v>
+        <v>122386328</v>
       </c>
       <c r="B15" t="n">
-        <v>57374</v>
+        <v>90819</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2079,50 +2088,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Låshålet, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>483057</v>
+        <v>483144</v>
       </c>
       <c r="R15" t="n">
-        <v>6989286</v>
+        <v>6989488</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2181,10 +2174,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122386311</v>
+        <v>122386314</v>
       </c>
       <c r="B16" t="n">
-        <v>57374</v>
+        <v>57379</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2215,16 +2208,28 @@
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Låshålet, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>483013</v>
+        <v>482998</v>
       </c>
       <c r="R16" t="n">
-        <v>6989190</v>
+        <v>6989231</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2257,11 +2262,6 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-01-30</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD16" t="b">

--- a/artfynd/A 60580-2024 artfynd.xlsx
+++ b/artfynd/A 60580-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122386317</v>
+        <v>122386314</v>
       </c>
       <c r="B2" t="n">
         <v>57379</v>
@@ -709,16 +709,28 @@
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Låshålet, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>483013</v>
+        <v>482998</v>
       </c>
       <c r="R2" t="n">
-        <v>6989410</v>
+        <v>6989231</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -751,11 +763,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-01-30</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,7 +789,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122386322</v>
+        <v>122386310</v>
       </c>
       <c r="B3" t="n">
         <v>57379</v>
@@ -822,10 +829,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>482807</v>
+        <v>483003</v>
       </c>
       <c r="R3" t="n">
-        <v>6989125</v>
+        <v>6989199</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -862,7 +869,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>ringhack färska</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -996,7 +1003,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122386315</v>
+        <v>122386311</v>
       </c>
       <c r="B5" t="n">
         <v>57379</v>
@@ -1029,33 +1036,17 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Låshålet, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>483057</v>
+        <v>483013</v>
       </c>
       <c r="R5" t="n">
-        <v>6989286</v>
+        <v>6989190</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1088,6 +1079,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-01-30</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1114,7 +1110,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122386318</v>
+        <v>122386313</v>
       </c>
       <c r="B6" t="n">
         <v>57379</v>
@@ -1154,10 +1150,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>482996</v>
+        <v>483001</v>
       </c>
       <c r="R6" t="n">
-        <v>6989426</v>
+        <v>6989219</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1194,7 +1190,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1221,10 +1217,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122386324</v>
+        <v>122386328</v>
       </c>
       <c r="B7" t="n">
-        <v>79732</v>
+        <v>90826</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1237,21 +1233,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6458</v>
+        <v>5432</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1261,10 +1257,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>483051</v>
+        <v>483144</v>
       </c>
       <c r="R7" t="n">
-        <v>6989494</v>
+        <v>6989488</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1537,7 +1533,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122386321</v>
+        <v>122386318</v>
       </c>
       <c r="B10" t="n">
         <v>57379</v>
@@ -1577,10 +1573,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>482832</v>
+        <v>482996</v>
       </c>
       <c r="R10" t="n">
-        <v>6989152</v>
+        <v>6989426</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1617,7 +1613,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>ringhack färska</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1644,7 +1640,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122386310</v>
+        <v>122386321</v>
       </c>
       <c r="B11" t="n">
         <v>57379</v>
@@ -1684,10 +1680,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>483003</v>
+        <v>482832</v>
       </c>
       <c r="R11" t="n">
-        <v>6989199</v>
+        <v>6989152</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1724,7 +1720,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1751,7 +1747,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122386313</v>
+        <v>122386315</v>
       </c>
       <c r="B12" t="n">
         <v>57379</v>
@@ -1784,17 +1780,33 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr"/>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Låshålet, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>483001</v>
+        <v>483057</v>
       </c>
       <c r="R12" t="n">
-        <v>6989219</v>
+        <v>6989286</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1827,11 +1839,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-01-30</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>ringhack</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1858,10 +1865,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122386319</v>
+        <v>122386324</v>
       </c>
       <c r="B13" t="n">
-        <v>57379</v>
+        <v>79732</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1874,21 +1881,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1898,10 +1905,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>482918</v>
+        <v>483051</v>
       </c>
       <c r="R13" t="n">
-        <v>6989264</v>
+        <v>6989494</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1934,11 +1941,6 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-01-30</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1965,7 +1967,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122386311</v>
+        <v>122386319</v>
       </c>
       <c r="B14" t="n">
         <v>57379</v>
@@ -2005,10 +2007,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>483013</v>
+        <v>482918</v>
       </c>
       <c r="R14" t="n">
-        <v>6989190</v>
+        <v>6989264</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2072,10 +2074,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122386328</v>
+        <v>122386317</v>
       </c>
       <c r="B15" t="n">
-        <v>90819</v>
+        <v>57379</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2088,21 +2090,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2112,10 +2114,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>483144</v>
+        <v>483013</v>
       </c>
       <c r="R15" t="n">
-        <v>6989488</v>
+        <v>6989410</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2148,6 +2150,11 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-01-30</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2174,7 +2181,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122386314</v>
+        <v>122386322</v>
       </c>
       <c r="B16" t="n">
         <v>57379</v>
@@ -2208,28 +2215,16 @@
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Låshålet, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>482998</v>
+        <v>482807</v>
       </c>
       <c r="R16" t="n">
-        <v>6989231</v>
+        <v>6989125</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2262,6 +2257,11 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-01-30</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>ringhack färska</t>
         </is>
       </c>
       <c r="AD16" t="b">

--- a/artfynd/A 60580-2024 artfynd.xlsx
+++ b/artfynd/A 60580-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122386314</v>
+        <v>122386310</v>
       </c>
       <c r="B2" t="n">
         <v>57379</v>
@@ -709,28 +709,16 @@
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Låshålet, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>482998</v>
+        <v>483003</v>
       </c>
       <c r="R2" t="n">
-        <v>6989231</v>
+        <v>6989199</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -763,6 +751,11 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-01-30</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -789,7 +782,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122386310</v>
+        <v>122386314</v>
       </c>
       <c r="B3" t="n">
         <v>57379</v>
@@ -823,16 +816,28 @@
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Låshålet, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>483003</v>
+        <v>482998</v>
       </c>
       <c r="R3" t="n">
-        <v>6989199</v>
+        <v>6989231</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -865,11 +870,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-01-30</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD3" t="b">

--- a/artfynd/A 60580-2024 artfynd.xlsx
+++ b/artfynd/A 60580-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122386310</v>
+        <v>122386323</v>
       </c>
       <c r="B2" t="n">
-        <v>57379</v>
+        <v>57395</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,16 +691,11 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
+        <v>100049</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>483003</v>
+        <v>483129</v>
       </c>
       <c r="R2" t="n">
-        <v>6989199</v>
+        <v>6989526</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -755,7 +750,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>hack</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,7 +777,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122386314</v>
+        <v>122386319</v>
       </c>
       <c r="B3" t="n">
         <v>57379</v>
@@ -800,11 +795,6 @@
       <c r="E3" t="n">
         <v>100109</v>
       </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
       <c r="G3" t="inlineStr">
         <is>
           <t>Picoides tridactylus</t>
@@ -816,28 +806,16 @@
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Låshålet, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>482998</v>
+        <v>482918</v>
       </c>
       <c r="R3" t="n">
-        <v>6989231</v>
+        <v>6989264</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -870,6 +848,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-01-30</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -896,7 +879,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122386316</v>
+        <v>122386321</v>
       </c>
       <c r="B4" t="n">
         <v>57379</v>
@@ -914,11 +897,6 @@
       <c r="E4" t="n">
         <v>100109</v>
       </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
       <c r="G4" t="inlineStr">
         <is>
           <t>Picoides tridactylus</t>
@@ -936,10 +914,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>483242</v>
+        <v>482832</v>
       </c>
       <c r="R4" t="n">
-        <v>6989315</v>
+        <v>6989152</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -976,7 +954,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1021,11 +999,6 @@
       <c r="E5" t="n">
         <v>100109</v>
       </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
       <c r="G5" t="inlineStr">
         <is>
           <t>Picoides tridactylus</t>
@@ -1110,7 +1083,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122386313</v>
+        <v>122386317</v>
       </c>
       <c r="B6" t="n">
         <v>57379</v>
@@ -1128,11 +1101,6 @@
       <c r="E6" t="n">
         <v>100109</v>
       </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
       <c r="G6" t="inlineStr">
         <is>
           <t>Picoides tridactylus</t>
@@ -1150,10 +1118,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>483001</v>
+        <v>483013</v>
       </c>
       <c r="R6" t="n">
-        <v>6989219</v>
+        <v>6989410</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1190,7 +1158,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>ringhack</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1217,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122386328</v>
+        <v>122386316</v>
       </c>
       <c r="B7" t="n">
-        <v>90826</v>
+        <v>57379</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1233,21 +1201,16 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5432</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>Granticka</t>
-        </is>
+        <v>100109</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1257,10 +1220,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>483144</v>
+        <v>483242</v>
       </c>
       <c r="R7" t="n">
-        <v>6989488</v>
+        <v>6989315</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1293,6 +1256,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-01-30</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1319,10 +1287,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122386323</v>
+        <v>122386313</v>
       </c>
       <c r="B8" t="n">
-        <v>57395</v>
+        <v>57379</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1335,16 +1303,11 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100049</v>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>Spillkråka</t>
-        </is>
+        <v>100109</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1359,10 +1322,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>483129</v>
+        <v>483001</v>
       </c>
       <c r="R8" t="n">
-        <v>6989526</v>
+        <v>6989219</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1399,7 +1362,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>hack</t>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1444,11 +1407,6 @@
       <c r="E9" t="n">
         <v>100109</v>
       </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
       <c r="G9" t="inlineStr">
         <is>
           <t>Picoides tridactylus</t>
@@ -1533,7 +1491,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122386318</v>
+        <v>122386315</v>
       </c>
       <c r="B10" t="n">
         <v>57379</v>
@@ -1551,11 +1509,6 @@
       <c r="E10" t="n">
         <v>100109</v>
       </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
       <c r="G10" t="inlineStr">
         <is>
           <t>Picoides tridactylus</t>
@@ -1566,17 +1519,33 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr"/>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Låshålet, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>482996</v>
+        <v>483057</v>
       </c>
       <c r="R10" t="n">
-        <v>6989426</v>
+        <v>6989286</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1609,11 +1578,6 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-01-30</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1640,10 +1604,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122386321</v>
+        <v>122386328</v>
       </c>
       <c r="B11" t="n">
-        <v>57379</v>
+        <v>90831</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1656,21 +1620,16 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
+        <v>5432</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1680,10 +1639,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>482832</v>
+        <v>483144</v>
       </c>
       <c r="R11" t="n">
-        <v>6989152</v>
+        <v>6989488</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1716,11 +1675,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-01-30</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>ringhack färska</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1747,7 +1701,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122386315</v>
+        <v>122386314</v>
       </c>
       <c r="B12" t="n">
         <v>57379</v>
@@ -1765,11 +1719,6 @@
       <c r="E12" t="n">
         <v>100109</v>
       </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
       <c r="G12" t="inlineStr">
         <is>
           <t>Picoides tridactylus</t>
@@ -1780,16 +1729,12 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>gammalt bo</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
@@ -1803,10 +1748,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>483057</v>
+        <v>482998</v>
       </c>
       <c r="R12" t="n">
-        <v>6989286</v>
+        <v>6989231</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1865,10 +1810,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122386324</v>
+        <v>122386322</v>
       </c>
       <c r="B13" t="n">
-        <v>79732</v>
+        <v>57379</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1881,21 +1826,16 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6458</v>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>Lunglav</t>
-        </is>
+        <v>100109</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1905,10 +1845,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>483051</v>
+        <v>482807</v>
       </c>
       <c r="R13" t="n">
-        <v>6989494</v>
+        <v>6989125</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1941,6 +1881,11 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-01-30</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>ringhack färska</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1967,7 +1912,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122386319</v>
+        <v>122386318</v>
       </c>
       <c r="B14" t="n">
         <v>57379</v>
@@ -1985,11 +1930,6 @@
       <c r="E14" t="n">
         <v>100109</v>
       </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
       <c r="G14" t="inlineStr">
         <is>
           <t>Picoides tridactylus</t>
@@ -2007,10 +1947,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>482918</v>
+        <v>482996</v>
       </c>
       <c r="R14" t="n">
-        <v>6989264</v>
+        <v>6989426</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2074,10 +2014,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122386317</v>
+        <v>122386324</v>
       </c>
       <c r="B15" t="n">
-        <v>57379</v>
+        <v>79733</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2090,21 +2030,16 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
+        <v>6458</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2114,10 +2049,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>483013</v>
+        <v>483051</v>
       </c>
       <c r="R15" t="n">
-        <v>6989410</v>
+        <v>6989494</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2150,11 +2085,6 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-01-30</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2181,7 +2111,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122386322</v>
+        <v>122386310</v>
       </c>
       <c r="B16" t="n">
         <v>57379</v>
@@ -2199,11 +2129,6 @@
       <c r="E16" t="n">
         <v>100109</v>
       </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
       <c r="G16" t="inlineStr">
         <is>
           <t>Picoides tridactylus</t>
@@ -2221,10 +2146,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>482807</v>
+        <v>483003</v>
       </c>
       <c r="R16" t="n">
-        <v>6989125</v>
+        <v>6989199</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2261,7 +2186,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>ringhack färska</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD16" t="b">

--- a/artfynd/A 60580-2024 artfynd.xlsx
+++ b/artfynd/A 60580-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122386323</v>
+        <v>122386310</v>
       </c>
       <c r="B2" t="n">
-        <v>57395</v>
+        <v>57383</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,11 +691,16 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>100109</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -710,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>483129</v>
+        <v>483003</v>
       </c>
       <c r="R2" t="n">
-        <v>6989526</v>
+        <v>6989199</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -750,7 +755,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>hack</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -780,7 +785,7 @@
         <v>122386319</v>
       </c>
       <c r="B3" t="n">
-        <v>57379</v>
+        <v>57383</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -794,6 +799,11 @@
       </c>
       <c r="E3" t="n">
         <v>100109</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -879,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122386321</v>
+        <v>122386317</v>
       </c>
       <c r="B4" t="n">
-        <v>57379</v>
+        <v>57383</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -897,6 +907,11 @@
       <c r="E4" t="n">
         <v>100109</v>
       </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
       <c r="G4" t="inlineStr">
         <is>
           <t>Picoides tridactylus</t>
@@ -914,10 +929,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>482832</v>
+        <v>483013</v>
       </c>
       <c r="R4" t="n">
-        <v>6989152</v>
+        <v>6989410</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -954,7 +969,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>ringhack färska</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -981,10 +996,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122386311</v>
+        <v>122386313</v>
       </c>
       <c r="B5" t="n">
-        <v>57379</v>
+        <v>57383</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -999,6 +1014,11 @@
       <c r="E5" t="n">
         <v>100109</v>
       </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
       <c r="G5" t="inlineStr">
         <is>
           <t>Picoides tridactylus</t>
@@ -1016,10 +1036,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>483013</v>
+        <v>483001</v>
       </c>
       <c r="R5" t="n">
-        <v>6989190</v>
+        <v>6989219</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1056,7 +1076,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1083,10 +1103,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122386317</v>
+        <v>122386321</v>
       </c>
       <c r="B6" t="n">
-        <v>57379</v>
+        <v>57383</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1101,6 +1121,11 @@
       <c r="E6" t="n">
         <v>100109</v>
       </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
       <c r="G6" t="inlineStr">
         <is>
           <t>Picoides tridactylus</t>
@@ -1118,10 +1143,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>483013</v>
+        <v>482832</v>
       </c>
       <c r="R6" t="n">
-        <v>6989410</v>
+        <v>6989152</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1158,7 +1183,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1185,10 +1210,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122386316</v>
+        <v>122386315</v>
       </c>
       <c r="B7" t="n">
-        <v>57379</v>
+        <v>57383</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1203,6 +1228,11 @@
       <c r="E7" t="n">
         <v>100109</v>
       </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
       <c r="G7" t="inlineStr">
         <is>
           <t>Picoides tridactylus</t>
@@ -1213,17 +1243,33 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr"/>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Låshålet, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>483242</v>
+        <v>483057</v>
       </c>
       <c r="R7" t="n">
-        <v>6989315</v>
+        <v>6989286</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1256,11 +1302,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-01-30</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1287,10 +1328,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122386313</v>
+        <v>122386311</v>
       </c>
       <c r="B8" t="n">
-        <v>57379</v>
+        <v>57383</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1305,6 +1346,11 @@
       <c r="E8" t="n">
         <v>100109</v>
       </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
       <c r="G8" t="inlineStr">
         <is>
           <t>Picoides tridactylus</t>
@@ -1322,10 +1368,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>483001</v>
+        <v>483013</v>
       </c>
       <c r="R8" t="n">
-        <v>6989219</v>
+        <v>6989190</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1362,7 +1408,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>ringhack</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1389,10 +1435,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122386320</v>
+        <v>122386314</v>
       </c>
       <c r="B9" t="n">
-        <v>57379</v>
+        <v>57383</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1407,6 +1453,11 @@
       <c r="E9" t="n">
         <v>100109</v>
       </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
       <c r="G9" t="inlineStr">
         <is>
           <t>Picoides tridactylus</t>
@@ -1418,16 +1469,28 @@
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Låshålet, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>482875</v>
+        <v>482998</v>
       </c>
       <c r="R9" t="n">
-        <v>6989223</v>
+        <v>6989231</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1460,11 +1523,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-01-30</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1491,10 +1549,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122386315</v>
+        <v>122386322</v>
       </c>
       <c r="B10" t="n">
-        <v>57379</v>
+        <v>57383</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1509,6 +1567,11 @@
       <c r="E10" t="n">
         <v>100109</v>
       </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
       <c r="G10" t="inlineStr">
         <is>
           <t>Picoides tridactylus</t>
@@ -1519,33 +1582,17 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Låshålet, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>483057</v>
+        <v>482807</v>
       </c>
       <c r="R10" t="n">
-        <v>6989286</v>
+        <v>6989125</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1578,6 +1625,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-01-30</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>ringhack färska</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1607,7 +1659,7 @@
         <v>122386328</v>
       </c>
       <c r="B11" t="n">
-        <v>90831</v>
+        <v>90844</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1621,6 +1673,11 @@
       </c>
       <c r="E11" t="n">
         <v>5432</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -1701,10 +1758,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122386314</v>
+        <v>122386324</v>
       </c>
       <c r="B12" t="n">
-        <v>57379</v>
+        <v>79737</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1717,41 +1774,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>6458</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Låshålet, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>482998</v>
+        <v>483051</v>
       </c>
       <c r="R12" t="n">
-        <v>6989231</v>
+        <v>6989494</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1810,10 +1860,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122386322</v>
+        <v>122386316</v>
       </c>
       <c r="B13" t="n">
-        <v>57379</v>
+        <v>57383</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1828,6 +1878,11 @@
       <c r="E13" t="n">
         <v>100109</v>
       </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
       <c r="G13" t="inlineStr">
         <is>
           <t>Picoides tridactylus</t>
@@ -1845,10 +1900,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>482807</v>
+        <v>483242</v>
       </c>
       <c r="R13" t="n">
-        <v>6989125</v>
+        <v>6989315</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1885,7 +1940,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>ringhack färska</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1912,10 +1967,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122386318</v>
+        <v>122386323</v>
       </c>
       <c r="B14" t="n">
-        <v>57379</v>
+        <v>57399</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1928,11 +1983,16 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>100049</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1947,10 +2007,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>482996</v>
+        <v>483129</v>
       </c>
       <c r="R14" t="n">
-        <v>6989426</v>
+        <v>6989526</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1987,7 +2047,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>hack</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2014,10 +2074,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122386324</v>
+        <v>122386320</v>
       </c>
       <c r="B15" t="n">
-        <v>79733</v>
+        <v>57383</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2030,16 +2090,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6458</v>
+        <v>100109</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2049,10 +2114,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>483051</v>
+        <v>482875</v>
       </c>
       <c r="R15" t="n">
-        <v>6989494</v>
+        <v>6989223</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2085,6 +2150,11 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-01-30</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2111,10 +2181,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122386310</v>
+        <v>122386318</v>
       </c>
       <c r="B16" t="n">
-        <v>57379</v>
+        <v>57383</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2129,6 +2199,11 @@
       <c r="E16" t="n">
         <v>100109</v>
       </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
       <c r="G16" t="inlineStr">
         <is>
           <t>Picoides tridactylus</t>
@@ -2146,10 +2221,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>483003</v>
+        <v>482996</v>
       </c>
       <c r="R16" t="n">
-        <v>6989199</v>
+        <v>6989426</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>

--- a/artfynd/A 60580-2024 artfynd.xlsx
+++ b/artfynd/A 60580-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122386310</v>
+        <v>122386318</v>
       </c>
       <c r="B2" t="n">
         <v>57383</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>483003</v>
+        <v>482996</v>
       </c>
       <c r="R2" t="n">
-        <v>6989199</v>
+        <v>6989426</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122386319</v>
+        <v>122386328</v>
       </c>
       <c r="B3" t="n">
-        <v>57383</v>
+        <v>90857</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,21 +798,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>482918</v>
+        <v>483144</v>
       </c>
       <c r="R3" t="n">
-        <v>6989264</v>
+        <v>6989488</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -858,11 +858,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-01-30</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,7 +884,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122386317</v>
+        <v>122386313</v>
       </c>
       <c r="B4" t="n">
         <v>57383</v>
@@ -929,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>483013</v>
+        <v>483001</v>
       </c>
       <c r="R4" t="n">
-        <v>6989410</v>
+        <v>6989219</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -969,7 +964,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -996,7 +991,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122386313</v>
+        <v>122386320</v>
       </c>
       <c r="B5" t="n">
         <v>57383</v>
@@ -1036,10 +1031,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>483001</v>
+        <v>482875</v>
       </c>
       <c r="R5" t="n">
-        <v>6989219</v>
+        <v>6989223</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1076,7 +1071,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>ringhack</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1103,10 +1098,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122386321</v>
+        <v>122386324</v>
       </c>
       <c r="B6" t="n">
-        <v>57383</v>
+        <v>79737</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1119,21 +1114,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1143,10 +1138,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>482832</v>
+        <v>483051</v>
       </c>
       <c r="R6" t="n">
-        <v>6989152</v>
+        <v>6989494</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1179,11 +1174,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-01-30</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>ringhack färska</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1210,7 +1200,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122386315</v>
+        <v>122386314</v>
       </c>
       <c r="B7" t="n">
         <v>57383</v>
@@ -1243,16 +1233,12 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>gammalt bo</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -1266,10 +1252,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>483057</v>
+        <v>482998</v>
       </c>
       <c r="R7" t="n">
-        <v>6989286</v>
+        <v>6989231</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1328,7 +1314,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122386311</v>
+        <v>122386317</v>
       </c>
       <c r="B8" t="n">
         <v>57383</v>
@@ -1371,7 +1357,7 @@
         <v>483013</v>
       </c>
       <c r="R8" t="n">
-        <v>6989190</v>
+        <v>6989410</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1435,7 +1421,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122386314</v>
+        <v>122386315</v>
       </c>
       <c r="B9" t="n">
         <v>57383</v>
@@ -1468,12 +1454,16 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr"/>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>gammalt bo</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1487,10 +1477,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>482998</v>
+        <v>483057</v>
       </c>
       <c r="R9" t="n">
-        <v>6989231</v>
+        <v>6989286</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1656,10 +1646,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122386328</v>
+        <v>122386323</v>
       </c>
       <c r="B11" t="n">
-        <v>90844</v>
+        <v>57399</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1672,21 +1662,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5432</v>
+        <v>100049</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1696,10 +1686,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>483144</v>
+        <v>483129</v>
       </c>
       <c r="R11" t="n">
-        <v>6989488</v>
+        <v>6989526</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1732,6 +1722,11 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-01-30</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>hack</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1758,10 +1753,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122386324</v>
+        <v>122386310</v>
       </c>
       <c r="B12" t="n">
-        <v>79737</v>
+        <v>57383</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1774,21 +1769,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1798,10 +1793,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>483051</v>
+        <v>483003</v>
       </c>
       <c r="R12" t="n">
-        <v>6989494</v>
+        <v>6989199</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1834,6 +1829,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-01-30</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1967,10 +1967,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122386323</v>
+        <v>122386321</v>
       </c>
       <c r="B14" t="n">
-        <v>57399</v>
+        <v>57383</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1983,16 +1983,16 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -2007,10 +2007,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>483129</v>
+        <v>482832</v>
       </c>
       <c r="R14" t="n">
-        <v>6989526</v>
+        <v>6989152</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2047,7 +2047,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>hack</t>
+          <t>ringhack färska</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2074,7 +2074,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122386320</v>
+        <v>122386311</v>
       </c>
       <c r="B15" t="n">
         <v>57383</v>
@@ -2114,10 +2114,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>482875</v>
+        <v>483013</v>
       </c>
       <c r="R15" t="n">
-        <v>6989223</v>
+        <v>6989190</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2154,7 +2154,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2181,7 +2181,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122386318</v>
+        <v>122386319</v>
       </c>
       <c r="B16" t="n">
         <v>57383</v>
@@ -2221,10 +2221,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>482996</v>
+        <v>482918</v>
       </c>
       <c r="R16" t="n">
-        <v>6989426</v>
+        <v>6989264</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>

--- a/artfynd/A 60580-2024 artfynd.xlsx
+++ b/artfynd/A 60580-2024 artfynd.xlsx
@@ -1646,10 +1646,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122386323</v>
+        <v>122386310</v>
       </c>
       <c r="B11" t="n">
-        <v>57399</v>
+        <v>57383</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1662,16 +1662,16 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1686,10 +1686,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>483129</v>
+        <v>483003</v>
       </c>
       <c r="R11" t="n">
-        <v>6989526</v>
+        <v>6989199</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1726,7 +1726,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>hack</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1753,10 +1753,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122386310</v>
+        <v>122386323</v>
       </c>
       <c r="B12" t="n">
-        <v>57383</v>
+        <v>57399</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1769,16 +1769,16 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1793,10 +1793,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>483003</v>
+        <v>483129</v>
       </c>
       <c r="R12" t="n">
-        <v>6989199</v>
+        <v>6989526</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1833,7 +1833,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>hack</t>
         </is>
       </c>
       <c r="AD12" t="b">

--- a/artfynd/A 60580-2024 artfynd.xlsx
+++ b/artfynd/A 60580-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122386318</v>
+        <v>122386319</v>
       </c>
       <c r="B2" t="n">
         <v>57383</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>482996</v>
+        <v>482918</v>
       </c>
       <c r="R2" t="n">
-        <v>6989426</v>
+        <v>6989264</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122386328</v>
+        <v>122386313</v>
       </c>
       <c r="B3" t="n">
-        <v>90857</v>
+        <v>57383</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,21 +798,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>483144</v>
+        <v>483001</v>
       </c>
       <c r="R3" t="n">
-        <v>6989488</v>
+        <v>6989219</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -858,6 +858,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-01-30</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -884,7 +889,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122386313</v>
+        <v>122386317</v>
       </c>
       <c r="B4" t="n">
         <v>57383</v>
@@ -924,10 +929,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>483001</v>
+        <v>483013</v>
       </c>
       <c r="R4" t="n">
-        <v>6989219</v>
+        <v>6989410</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -964,7 +969,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>ringhack</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -991,7 +996,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122386320</v>
+        <v>122386314</v>
       </c>
       <c r="B5" t="n">
         <v>57383</v>
@@ -1025,16 +1030,28 @@
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Låshålet, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>482875</v>
+        <v>482998</v>
       </c>
       <c r="R5" t="n">
-        <v>6989223</v>
+        <v>6989231</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1067,11 +1084,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-01-30</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1098,10 +1110,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122386324</v>
+        <v>122386310</v>
       </c>
       <c r="B6" t="n">
-        <v>79737</v>
+        <v>57383</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1114,21 +1126,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1138,10 +1150,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>483051</v>
+        <v>483003</v>
       </c>
       <c r="R6" t="n">
-        <v>6989494</v>
+        <v>6989199</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1174,6 +1186,11 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-01-30</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1200,10 +1217,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122386314</v>
+        <v>122386324</v>
       </c>
       <c r="B7" t="n">
-        <v>57383</v>
+        <v>79737</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1216,46 +1233,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Låshålet, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>482998</v>
+        <v>483051</v>
       </c>
       <c r="R7" t="n">
-        <v>6989231</v>
+        <v>6989494</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1314,7 +1319,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122386317</v>
+        <v>122386318</v>
       </c>
       <c r="B8" t="n">
         <v>57383</v>
@@ -1354,10 +1359,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>483013</v>
+        <v>482996</v>
       </c>
       <c r="R8" t="n">
-        <v>6989410</v>
+        <v>6989426</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1421,7 +1426,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122386315</v>
+        <v>122386321</v>
       </c>
       <c r="B9" t="n">
         <v>57383</v>
@@ -1454,33 +1459,17 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Låshålet, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>483057</v>
+        <v>482832</v>
       </c>
       <c r="R9" t="n">
-        <v>6989286</v>
+        <v>6989152</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1513,6 +1502,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-01-30</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>ringhack färska</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1539,7 +1533,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122386322</v>
+        <v>122386315</v>
       </c>
       <c r="B10" t="n">
         <v>57383</v>
@@ -1572,17 +1566,33 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr"/>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Låshålet, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>482807</v>
+        <v>483057</v>
       </c>
       <c r="R10" t="n">
-        <v>6989125</v>
+        <v>6989286</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1615,11 +1625,6 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-01-30</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>ringhack färska</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1646,7 +1651,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122386310</v>
+        <v>122386320</v>
       </c>
       <c r="B11" t="n">
         <v>57383</v>
@@ -1686,10 +1691,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>483003</v>
+        <v>482875</v>
       </c>
       <c r="R11" t="n">
-        <v>6989199</v>
+        <v>6989223</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1726,7 +1731,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1967,7 +1972,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122386321</v>
+        <v>122386322</v>
       </c>
       <c r="B14" t="n">
         <v>57383</v>
@@ -2007,10 +2012,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>482832</v>
+        <v>482807</v>
       </c>
       <c r="R14" t="n">
-        <v>6989152</v>
+        <v>6989125</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2181,10 +2186,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122386319</v>
+        <v>122386328</v>
       </c>
       <c r="B16" t="n">
-        <v>57383</v>
+        <v>90857</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2197,21 +2202,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2221,10 +2226,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>482918</v>
+        <v>483144</v>
       </c>
       <c r="R16" t="n">
-        <v>6989264</v>
+        <v>6989488</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2257,11 +2262,6 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-01-30</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD16" t="b">

--- a/artfynd/A 60580-2024 artfynd.xlsx
+++ b/artfynd/A 60580-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122386319</v>
+        <v>122386320</v>
       </c>
       <c r="B2" t="n">
         <v>57383</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>482918</v>
+        <v>482875</v>
       </c>
       <c r="R2" t="n">
-        <v>6989264</v>
+        <v>6989223</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -755,7 +755,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,7 +782,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122386313</v>
+        <v>122386310</v>
       </c>
       <c r="B3" t="n">
         <v>57383</v>
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>483001</v>
+        <v>483003</v>
       </c>
       <c r="R3" t="n">
-        <v>6989219</v>
+        <v>6989199</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -862,7 +862,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>ringhack</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,7 +889,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122386317</v>
+        <v>122386315</v>
       </c>
       <c r="B4" t="n">
         <v>57383</v>
@@ -922,17 +922,33 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr"/>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Låshålet, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>483013</v>
+        <v>483057</v>
       </c>
       <c r="R4" t="n">
-        <v>6989410</v>
+        <v>6989286</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -965,11 +981,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-01-30</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -996,7 +1007,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122386314</v>
+        <v>122386319</v>
       </c>
       <c r="B5" t="n">
         <v>57383</v>
@@ -1030,28 +1041,16 @@
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Låshålet, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>482998</v>
+        <v>482918</v>
       </c>
       <c r="R5" t="n">
-        <v>6989231</v>
+        <v>6989264</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1084,6 +1083,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-01-30</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1110,7 +1114,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122386310</v>
+        <v>122386321</v>
       </c>
       <c r="B6" t="n">
         <v>57383</v>
@@ -1150,10 +1154,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>483003</v>
+        <v>482832</v>
       </c>
       <c r="R6" t="n">
-        <v>6989199</v>
+        <v>6989152</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1190,7 +1194,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1217,10 +1221,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122386324</v>
+        <v>122386322</v>
       </c>
       <c r="B7" t="n">
-        <v>79737</v>
+        <v>57383</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1233,21 +1237,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1257,10 +1261,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>483051</v>
+        <v>482807</v>
       </c>
       <c r="R7" t="n">
-        <v>6989494</v>
+        <v>6989125</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1293,6 +1297,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-01-30</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>ringhack färska</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1319,10 +1328,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122386318</v>
+        <v>122386328</v>
       </c>
       <c r="B8" t="n">
-        <v>57383</v>
+        <v>90851</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1335,21 +1344,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1359,10 +1368,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>482996</v>
+        <v>483144</v>
       </c>
       <c r="R8" t="n">
-        <v>6989426</v>
+        <v>6989488</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1395,11 +1404,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-01-30</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1426,7 +1430,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122386321</v>
+        <v>122386313</v>
       </c>
       <c r="B9" t="n">
         <v>57383</v>
@@ -1466,10 +1470,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>482832</v>
+        <v>483001</v>
       </c>
       <c r="R9" t="n">
-        <v>6989152</v>
+        <v>6989219</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1506,7 +1510,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>ringhack färska</t>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1533,7 +1537,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122386315</v>
+        <v>122386316</v>
       </c>
       <c r="B10" t="n">
         <v>57383</v>
@@ -1566,33 +1570,17 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Låshålet, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>483057</v>
+        <v>483242</v>
       </c>
       <c r="R10" t="n">
-        <v>6989286</v>
+        <v>6989315</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1625,6 +1613,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-01-30</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1651,7 +1644,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122386320</v>
+        <v>122386318</v>
       </c>
       <c r="B11" t="n">
         <v>57383</v>
@@ -1691,10 +1684,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>482875</v>
+        <v>482996</v>
       </c>
       <c r="R11" t="n">
-        <v>6989223</v>
+        <v>6989426</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1731,7 +1724,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1758,10 +1751,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122386323</v>
+        <v>122386324</v>
       </c>
       <c r="B12" t="n">
-        <v>57399</v>
+        <v>79737</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1774,21 +1767,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100049</v>
+        <v>6458</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1798,10 +1791,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>483129</v>
+        <v>483051</v>
       </c>
       <c r="R12" t="n">
-        <v>6989526</v>
+        <v>6989494</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1834,11 +1827,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-01-30</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>hack</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1865,7 +1853,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122386316</v>
+        <v>122386317</v>
       </c>
       <c r="B13" t="n">
         <v>57383</v>
@@ -1905,10 +1893,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>483242</v>
+        <v>483013</v>
       </c>
       <c r="R13" t="n">
-        <v>6989315</v>
+        <v>6989410</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1972,7 +1960,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122386322</v>
+        <v>122386314</v>
       </c>
       <c r="B14" t="n">
         <v>57383</v>
@@ -2006,16 +1994,28 @@
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Låshålet, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>482807</v>
+        <v>482998</v>
       </c>
       <c r="R14" t="n">
-        <v>6989125</v>
+        <v>6989231</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2048,11 +2048,6 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-01-30</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>ringhack färska</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2079,10 +2074,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122386311</v>
+        <v>122386323</v>
       </c>
       <c r="B15" t="n">
-        <v>57383</v>
+        <v>57399</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2095,16 +2090,16 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -2119,10 +2114,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>483013</v>
+        <v>483129</v>
       </c>
       <c r="R15" t="n">
-        <v>6989190</v>
+        <v>6989526</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2159,7 +2154,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>hack</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2186,10 +2181,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122386328</v>
+        <v>122386311</v>
       </c>
       <c r="B16" t="n">
-        <v>90857</v>
+        <v>57383</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2202,21 +2197,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2226,10 +2221,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>483144</v>
+        <v>483013</v>
       </c>
       <c r="R16" t="n">
-        <v>6989488</v>
+        <v>6989190</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2262,6 +2257,11 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-01-30</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD16" t="b">

--- a/artfynd/A 60580-2024 artfynd.xlsx
+++ b/artfynd/A 60580-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122386320</v>
+        <v>122386322</v>
       </c>
       <c r="B2" t="n">
         <v>57383</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>482875</v>
+        <v>482807</v>
       </c>
       <c r="R2" t="n">
-        <v>6989223</v>
+        <v>6989125</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -755,7 +755,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack färska</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,7 +782,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122386310</v>
+        <v>122386313</v>
       </c>
       <c r="B3" t="n">
         <v>57383</v>
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>483003</v>
+        <v>483001</v>
       </c>
       <c r="R3" t="n">
-        <v>6989199</v>
+        <v>6989219</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -862,7 +862,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,7 +889,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122386315</v>
+        <v>122386319</v>
       </c>
       <c r="B4" t="n">
         <v>57383</v>
@@ -922,33 +922,17 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Låshålet, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>483057</v>
+        <v>482918</v>
       </c>
       <c r="R4" t="n">
-        <v>6989286</v>
+        <v>6989264</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,6 +965,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-01-30</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1007,10 +996,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122386319</v>
+        <v>122386323</v>
       </c>
       <c r="B5" t="n">
-        <v>57383</v>
+        <v>57399</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1023,16 +1012,16 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1047,10 +1036,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>482918</v>
+        <v>483129</v>
       </c>
       <c r="R5" t="n">
-        <v>6989264</v>
+        <v>6989526</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1087,7 +1076,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>hack</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1114,7 +1103,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122386321</v>
+        <v>122386320</v>
       </c>
       <c r="B6" t="n">
         <v>57383</v>
@@ -1154,10 +1143,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>482832</v>
+        <v>482875</v>
       </c>
       <c r="R6" t="n">
-        <v>6989152</v>
+        <v>6989223</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1194,7 +1183,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>ringhack färska</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1221,7 +1210,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122386322</v>
+        <v>122386315</v>
       </c>
       <c r="B7" t="n">
         <v>57383</v>
@@ -1254,17 +1243,33 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr"/>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Låshålet, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>482807</v>
+        <v>483057</v>
       </c>
       <c r="R7" t="n">
-        <v>6989125</v>
+        <v>6989286</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1297,11 +1302,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-01-30</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>ringhack färska</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1328,10 +1328,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122386328</v>
+        <v>122386321</v>
       </c>
       <c r="B8" t="n">
-        <v>90851</v>
+        <v>57383</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1344,21 +1344,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1368,10 +1368,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>483144</v>
+        <v>482832</v>
       </c>
       <c r="R8" t="n">
-        <v>6989488</v>
+        <v>6989152</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1404,6 +1404,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-01-30</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>ringhack färska</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1430,7 +1435,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122386313</v>
+        <v>122386311</v>
       </c>
       <c r="B9" t="n">
         <v>57383</v>
@@ -1470,10 +1475,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>483001</v>
+        <v>483013</v>
       </c>
       <c r="R9" t="n">
-        <v>6989219</v>
+        <v>6989190</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1510,7 +1515,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>ringhack</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1537,7 +1542,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122386316</v>
+        <v>122386317</v>
       </c>
       <c r="B10" t="n">
         <v>57383</v>
@@ -1577,10 +1582,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>483242</v>
+        <v>483013</v>
       </c>
       <c r="R10" t="n">
-        <v>6989315</v>
+        <v>6989410</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1644,10 +1649,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122386318</v>
+        <v>122386328</v>
       </c>
       <c r="B11" t="n">
-        <v>57383</v>
+        <v>90851</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1660,21 +1665,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1684,10 +1689,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>482996</v>
+        <v>483144</v>
       </c>
       <c r="R11" t="n">
-        <v>6989426</v>
+        <v>6989488</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1720,11 +1725,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-01-30</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1751,10 +1751,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122386324</v>
+        <v>122386316</v>
       </c>
       <c r="B12" t="n">
-        <v>79737</v>
+        <v>57383</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1767,21 +1767,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1791,10 +1791,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>483051</v>
+        <v>483242</v>
       </c>
       <c r="R12" t="n">
-        <v>6989494</v>
+        <v>6989315</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1827,6 +1827,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-01-30</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1853,7 +1858,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122386317</v>
+        <v>122386314</v>
       </c>
       <c r="B13" t="n">
         <v>57383</v>
@@ -1887,16 +1892,28 @@
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Låshålet, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>483013</v>
+        <v>482998</v>
       </c>
       <c r="R13" t="n">
-        <v>6989410</v>
+        <v>6989231</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1929,11 +1946,6 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-01-30</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1960,7 +1972,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122386314</v>
+        <v>122386310</v>
       </c>
       <c r="B14" t="n">
         <v>57383</v>
@@ -1994,28 +2006,16 @@
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Låshålet, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>482998</v>
+        <v>483003</v>
       </c>
       <c r="R14" t="n">
-        <v>6989231</v>
+        <v>6989199</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2048,6 +2048,11 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-01-30</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2074,10 +2079,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122386323</v>
+        <v>122386318</v>
       </c>
       <c r="B15" t="n">
-        <v>57399</v>
+        <v>57383</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2090,16 +2095,16 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -2114,10 +2119,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>483129</v>
+        <v>482996</v>
       </c>
       <c r="R15" t="n">
-        <v>6989526</v>
+        <v>6989426</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2154,7 +2159,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>hack</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2181,10 +2186,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122386311</v>
+        <v>122386324</v>
       </c>
       <c r="B16" t="n">
-        <v>57383</v>
+        <v>79737</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2197,21 +2202,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2221,10 +2226,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>483013</v>
+        <v>483051</v>
       </c>
       <c r="R16" t="n">
-        <v>6989190</v>
+        <v>6989494</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2257,11 +2262,6 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-01-30</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD16" t="b">

--- a/artfynd/A 60580-2024 artfynd.xlsx
+++ b/artfynd/A 60580-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122386322</v>
+        <v>122386310</v>
       </c>
       <c r="B2" t="n">
-        <v>57383</v>
+        <v>57384</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>482807</v>
+        <v>483003</v>
       </c>
       <c r="R2" t="n">
-        <v>6989125</v>
+        <v>6989199</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -755,7 +755,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>ringhack färska</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122386313</v>
+        <v>122386319</v>
       </c>
       <c r="B3" t="n">
-        <v>57383</v>
+        <v>57384</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>483001</v>
+        <v>482918</v>
       </c>
       <c r="R3" t="n">
-        <v>6989219</v>
+        <v>6989264</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -862,7 +862,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>ringhack</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122386319</v>
+        <v>122386328</v>
       </c>
       <c r="B4" t="n">
-        <v>57383</v>
+        <v>90852</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -905,21 +905,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -929,10 +929,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>482918</v>
+        <v>483144</v>
       </c>
       <c r="R4" t="n">
-        <v>6989264</v>
+        <v>6989488</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -965,11 +965,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-01-30</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -999,7 +994,7 @@
         <v>122386323</v>
       </c>
       <c r="B5" t="n">
-        <v>57399</v>
+        <v>57400</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1103,10 +1098,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122386320</v>
+        <v>122386322</v>
       </c>
       <c r="B6" t="n">
-        <v>57383</v>
+        <v>57384</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1143,10 +1138,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>482875</v>
+        <v>482807</v>
       </c>
       <c r="R6" t="n">
-        <v>6989223</v>
+        <v>6989125</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1183,7 +1178,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack färska</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1210,10 +1205,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122386315</v>
+        <v>122386313</v>
       </c>
       <c r="B7" t="n">
-        <v>57383</v>
+        <v>57384</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1243,33 +1238,17 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Låshålet, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>483057</v>
+        <v>483001</v>
       </c>
       <c r="R7" t="n">
-        <v>6989286</v>
+        <v>6989219</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1302,6 +1281,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-01-30</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1328,10 +1312,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122386321</v>
+        <v>122386311</v>
       </c>
       <c r="B8" t="n">
-        <v>57383</v>
+        <v>57384</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1368,10 +1352,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>482832</v>
+        <v>483013</v>
       </c>
       <c r="R8" t="n">
-        <v>6989152</v>
+        <v>6989190</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1408,7 +1392,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>ringhack färska</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1435,10 +1419,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122386311</v>
+        <v>122386318</v>
       </c>
       <c r="B9" t="n">
-        <v>57383</v>
+        <v>57384</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1475,10 +1459,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>483013</v>
+        <v>482996</v>
       </c>
       <c r="R9" t="n">
-        <v>6989190</v>
+        <v>6989426</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1542,10 +1526,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122386317</v>
+        <v>122386320</v>
       </c>
       <c r="B10" t="n">
-        <v>57383</v>
+        <v>57384</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1582,10 +1566,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>483013</v>
+        <v>482875</v>
       </c>
       <c r="R10" t="n">
-        <v>6989410</v>
+        <v>6989223</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1622,7 +1606,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1649,10 +1633,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122386328</v>
+        <v>122386324</v>
       </c>
       <c r="B11" t="n">
-        <v>90851</v>
+        <v>79738</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1665,21 +1649,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5432</v>
+        <v>6458</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1689,10 +1673,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>483144</v>
+        <v>483051</v>
       </c>
       <c r="R11" t="n">
-        <v>6989488</v>
+        <v>6989494</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1751,10 +1735,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122386316</v>
+        <v>122386317</v>
       </c>
       <c r="B12" t="n">
-        <v>57383</v>
+        <v>57384</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1791,10 +1775,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>483242</v>
+        <v>483013</v>
       </c>
       <c r="R12" t="n">
-        <v>6989315</v>
+        <v>6989410</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1858,10 +1842,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122386314</v>
+        <v>122386316</v>
       </c>
       <c r="B13" t="n">
-        <v>57383</v>
+        <v>57384</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1892,28 +1876,16 @@
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Låshålet, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>482998</v>
+        <v>483242</v>
       </c>
       <c r="R13" t="n">
-        <v>6989231</v>
+        <v>6989315</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1946,6 +1918,11 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-01-30</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1972,10 +1949,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122386310</v>
+        <v>122386314</v>
       </c>
       <c r="B14" t="n">
-        <v>57383</v>
+        <v>57384</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2006,16 +1983,28 @@
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Låshålet, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>483003</v>
+        <v>482998</v>
       </c>
       <c r="R14" t="n">
-        <v>6989199</v>
+        <v>6989231</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2048,11 +2037,6 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-01-30</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2079,10 +2063,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122386318</v>
+        <v>122386321</v>
       </c>
       <c r="B15" t="n">
-        <v>57383</v>
+        <v>57384</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2119,10 +2103,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>482996</v>
+        <v>482832</v>
       </c>
       <c r="R15" t="n">
-        <v>6989426</v>
+        <v>6989152</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2159,7 +2143,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2186,10 +2170,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122386324</v>
+        <v>122386315</v>
       </c>
       <c r="B16" t="n">
-        <v>79737</v>
+        <v>57384</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2202,34 +2186,50 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Låshålet, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>483051</v>
+        <v>483057</v>
       </c>
       <c r="R16" t="n">
-        <v>6989494</v>
+        <v>6989286</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>

--- a/artfynd/A 60580-2024 artfynd.xlsx
+++ b/artfynd/A 60580-2024 artfynd.xlsx
@@ -1419,7 +1419,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122386318</v>
+        <v>122386320</v>
       </c>
       <c r="B9" t="n">
         <v>57384</v>
@@ -1459,10 +1459,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>482996</v>
+        <v>482875</v>
       </c>
       <c r="R9" t="n">
-        <v>6989426</v>
+        <v>6989223</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1499,7 +1499,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1526,7 +1526,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122386320</v>
+        <v>122386318</v>
       </c>
       <c r="B10" t="n">
         <v>57384</v>
@@ -1566,10 +1566,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>482875</v>
+        <v>482996</v>
       </c>
       <c r="R10" t="n">
-        <v>6989223</v>
+        <v>6989426</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1606,7 +1606,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD10" t="b">

--- a/artfynd/A 60580-2024 artfynd.xlsx
+++ b/artfynd/A 60580-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122386310</v>
+        <v>122386321</v>
       </c>
       <c r="B2" t="n">
         <v>57384</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>483003</v>
+        <v>482832</v>
       </c>
       <c r="R2" t="n">
-        <v>6989199</v>
+        <v>6989152</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -755,7 +755,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,7 +782,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122386319</v>
+        <v>122386318</v>
       </c>
       <c r="B3" t="n">
         <v>57384</v>
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>482918</v>
+        <v>482996</v>
       </c>
       <c r="R3" t="n">
-        <v>6989264</v>
+        <v>6989426</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -889,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122386328</v>
+        <v>122386315</v>
       </c>
       <c r="B4" t="n">
-        <v>90852</v>
+        <v>57384</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -905,34 +905,50 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Låshålet, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>483144</v>
+        <v>483057</v>
       </c>
       <c r="R4" t="n">
-        <v>6989488</v>
+        <v>6989286</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -991,10 +1007,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122386323</v>
+        <v>122386311</v>
       </c>
       <c r="B5" t="n">
-        <v>57400</v>
+        <v>57384</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1007,16 +1023,16 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1031,10 +1047,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>483129</v>
+        <v>483013</v>
       </c>
       <c r="R5" t="n">
-        <v>6989526</v>
+        <v>6989190</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1071,7 +1087,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>hack</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1098,7 +1114,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122386322</v>
+        <v>122386313</v>
       </c>
       <c r="B6" t="n">
         <v>57384</v>
@@ -1138,10 +1154,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>482807</v>
+        <v>483001</v>
       </c>
       <c r="R6" t="n">
-        <v>6989125</v>
+        <v>6989219</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1178,7 +1194,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>ringhack färska</t>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1205,7 +1221,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122386313</v>
+        <v>122386316</v>
       </c>
       <c r="B7" t="n">
         <v>57384</v>
@@ -1245,10 +1261,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>483001</v>
+        <v>483242</v>
       </c>
       <c r="R7" t="n">
-        <v>6989219</v>
+        <v>6989315</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1285,7 +1301,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>ringhack</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1312,10 +1328,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122386311</v>
+        <v>122386328</v>
       </c>
       <c r="B8" t="n">
-        <v>57384</v>
+        <v>90855</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1328,21 +1344,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1352,10 +1368,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>483013</v>
+        <v>483144</v>
       </c>
       <c r="R8" t="n">
-        <v>6989190</v>
+        <v>6989488</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1388,11 +1404,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-01-30</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1526,10 +1537,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122386318</v>
+        <v>122386324</v>
       </c>
       <c r="B10" t="n">
-        <v>57384</v>
+        <v>79741</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1542,21 +1553,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1566,10 +1577,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>482996</v>
+        <v>483051</v>
       </c>
       <c r="R10" t="n">
-        <v>6989426</v>
+        <v>6989494</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1602,11 +1613,6 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-01-30</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1633,10 +1639,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122386324</v>
+        <v>122386319</v>
       </c>
       <c r="B11" t="n">
-        <v>79738</v>
+        <v>57384</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1649,21 +1655,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1673,10 +1679,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>483051</v>
+        <v>482918</v>
       </c>
       <c r="R11" t="n">
-        <v>6989494</v>
+        <v>6989264</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1709,6 +1715,11 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-01-30</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1735,7 +1746,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122386317</v>
+        <v>122386322</v>
       </c>
       <c r="B12" t="n">
         <v>57384</v>
@@ -1775,10 +1786,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>483013</v>
+        <v>482807</v>
       </c>
       <c r="R12" t="n">
-        <v>6989410</v>
+        <v>6989125</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1815,7 +1826,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1842,7 +1853,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122386316</v>
+        <v>122386310</v>
       </c>
       <c r="B13" t="n">
         <v>57384</v>
@@ -1882,10 +1893,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>483242</v>
+        <v>483003</v>
       </c>
       <c r="R13" t="n">
-        <v>6989315</v>
+        <v>6989199</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2063,10 +2074,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122386321</v>
+        <v>122386323</v>
       </c>
       <c r="B15" t="n">
-        <v>57384</v>
+        <v>57400</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2079,16 +2090,16 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -2103,10 +2114,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>482832</v>
+        <v>483129</v>
       </c>
       <c r="R15" t="n">
-        <v>6989152</v>
+        <v>6989526</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2143,7 +2154,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>ringhack färska</t>
+          <t>hack</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2170,7 +2181,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122386315</v>
+        <v>122386317</v>
       </c>
       <c r="B16" t="n">
         <v>57384</v>
@@ -2203,33 +2214,17 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Låshålet, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>483057</v>
+        <v>483013</v>
       </c>
       <c r="R16" t="n">
-        <v>6989286</v>
+        <v>6989410</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2262,6 +2257,11 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-01-30</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD16" t="b">

--- a/artfynd/A 60580-2024 artfynd.xlsx
+++ b/artfynd/A 60580-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122386321</v>
+        <v>122386320</v>
       </c>
       <c r="B2" t="n">
         <v>57384</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>482832</v>
+        <v>482875</v>
       </c>
       <c r="R2" t="n">
-        <v>6989152</v>
+        <v>6989223</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -755,7 +755,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>ringhack färska</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,7 +782,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122386318</v>
+        <v>122386321</v>
       </c>
       <c r="B3" t="n">
         <v>57384</v>
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>482996</v>
+        <v>482832</v>
       </c>
       <c r="R3" t="n">
-        <v>6989426</v>
+        <v>6989152</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -862,7 +862,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,7 +889,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122386315</v>
+        <v>122386319</v>
       </c>
       <c r="B4" t="n">
         <v>57384</v>
@@ -922,33 +922,17 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Låshålet, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>483057</v>
+        <v>482918</v>
       </c>
       <c r="R4" t="n">
-        <v>6989286</v>
+        <v>6989264</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,6 +965,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-01-30</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1007,10 +996,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122386311</v>
+        <v>122386324</v>
       </c>
       <c r="B5" t="n">
-        <v>57384</v>
+        <v>79741</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1023,21 +1012,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1047,10 +1036,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>483013</v>
+        <v>483051</v>
       </c>
       <c r="R5" t="n">
-        <v>6989190</v>
+        <v>6989494</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1083,11 +1072,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-01-30</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1114,7 +1098,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122386313</v>
+        <v>122386310</v>
       </c>
       <c r="B6" t="n">
         <v>57384</v>
@@ -1154,10 +1138,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>483001</v>
+        <v>483003</v>
       </c>
       <c r="R6" t="n">
-        <v>6989219</v>
+        <v>6989199</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1194,7 +1178,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>ringhack</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1221,7 +1205,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122386316</v>
+        <v>122386317</v>
       </c>
       <c r="B7" t="n">
         <v>57384</v>
@@ -1261,10 +1245,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>483242</v>
+        <v>483013</v>
       </c>
       <c r="R7" t="n">
-        <v>6989315</v>
+        <v>6989410</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1328,10 +1312,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122386328</v>
+        <v>122386311</v>
       </c>
       <c r="B8" t="n">
-        <v>90855</v>
+        <v>57384</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1344,21 +1328,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1368,10 +1352,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>483144</v>
+        <v>483013</v>
       </c>
       <c r="R8" t="n">
-        <v>6989488</v>
+        <v>6989190</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1404,6 +1388,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-01-30</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1430,7 +1419,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122386320</v>
+        <v>122386313</v>
       </c>
       <c r="B9" t="n">
         <v>57384</v>
@@ -1470,10 +1459,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>482875</v>
+        <v>483001</v>
       </c>
       <c r="R9" t="n">
-        <v>6989223</v>
+        <v>6989219</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1510,7 +1499,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1537,10 +1526,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122386324</v>
+        <v>122386323</v>
       </c>
       <c r="B10" t="n">
-        <v>79741</v>
+        <v>57400</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1553,21 +1542,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6458</v>
+        <v>100049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1577,10 +1566,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>483051</v>
+        <v>483129</v>
       </c>
       <c r="R10" t="n">
-        <v>6989494</v>
+        <v>6989526</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1613,6 +1602,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-01-30</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>hack</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1639,7 +1633,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122386319</v>
+        <v>122386316</v>
       </c>
       <c r="B11" t="n">
         <v>57384</v>
@@ -1679,10 +1673,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>482918</v>
+        <v>483242</v>
       </c>
       <c r="R11" t="n">
-        <v>6989264</v>
+        <v>6989315</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1853,7 +1847,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122386310</v>
+        <v>122386318</v>
       </c>
       <c r="B13" t="n">
         <v>57384</v>
@@ -1893,10 +1887,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>483003</v>
+        <v>482996</v>
       </c>
       <c r="R13" t="n">
-        <v>6989199</v>
+        <v>6989426</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1960,7 +1954,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122386314</v>
+        <v>122386315</v>
       </c>
       <c r="B14" t="n">
         <v>57384</v>
@@ -1993,12 +1987,16 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr"/>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
-          <t>gammalt bo</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
@@ -2012,10 +2010,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>482998</v>
+        <v>483057</v>
       </c>
       <c r="R14" t="n">
-        <v>6989231</v>
+        <v>6989286</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2074,10 +2072,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122386323</v>
+        <v>122386314</v>
       </c>
       <c r="B15" t="n">
-        <v>57400</v>
+        <v>57384</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2090,16 +2088,16 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -2108,16 +2106,28 @@
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Låshålet, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>483129</v>
+        <v>482998</v>
       </c>
       <c r="R15" t="n">
-        <v>6989526</v>
+        <v>6989231</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2150,11 +2160,6 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-01-30</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>hack</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2181,10 +2186,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122386317</v>
+        <v>122386328</v>
       </c>
       <c r="B16" t="n">
-        <v>57384</v>
+        <v>90855</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2197,21 +2202,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2221,10 +2226,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>483013</v>
+        <v>483144</v>
       </c>
       <c r="R16" t="n">
-        <v>6989410</v>
+        <v>6989488</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2257,11 +2262,6 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-01-30</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD16" t="b">

--- a/artfynd/A 60580-2024 artfynd.xlsx
+++ b/artfynd/A 60580-2024 artfynd.xlsx
@@ -1312,10 +1312,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122386311</v>
+        <v>122386323</v>
       </c>
       <c r="B8" t="n">
-        <v>57384</v>
+        <v>57400</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1328,16 +1328,16 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1352,10 +1352,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>483013</v>
+        <v>483129</v>
       </c>
       <c r="R8" t="n">
-        <v>6989190</v>
+        <v>6989526</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1392,7 +1392,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>hack</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1419,7 +1419,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122386313</v>
+        <v>122386311</v>
       </c>
       <c r="B9" t="n">
         <v>57384</v>
@@ -1459,10 +1459,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>483001</v>
+        <v>483013</v>
       </c>
       <c r="R9" t="n">
-        <v>6989219</v>
+        <v>6989190</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1499,7 +1499,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>ringhack</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1526,10 +1526,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122386323</v>
+        <v>122386313</v>
       </c>
       <c r="B10" t="n">
-        <v>57400</v>
+        <v>57384</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1542,16 +1542,16 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1566,10 +1566,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>483129</v>
+        <v>483001</v>
       </c>
       <c r="R10" t="n">
-        <v>6989526</v>
+        <v>6989219</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1606,7 +1606,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>hack</t>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD10" t="b">

--- a/artfynd/A 60580-2024 artfynd.xlsx
+++ b/artfynd/A 60580-2024 artfynd.xlsx
@@ -889,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122386319</v>
+        <v>122386324</v>
       </c>
       <c r="B4" t="n">
-        <v>57384</v>
+        <v>79741</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -905,21 +905,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -929,10 +929,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>482918</v>
+        <v>483051</v>
       </c>
       <c r="R4" t="n">
-        <v>6989264</v>
+        <v>6989494</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -965,11 +965,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-01-30</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -996,10 +991,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122386324</v>
+        <v>122386319</v>
       </c>
       <c r="B5" t="n">
-        <v>79741</v>
+        <v>57384</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1012,21 +1007,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1036,10 +1031,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>483051</v>
+        <v>482918</v>
       </c>
       <c r="R5" t="n">
-        <v>6989494</v>
+        <v>6989264</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1072,6 +1067,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-01-30</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1312,10 +1312,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122386323</v>
+        <v>122386311</v>
       </c>
       <c r="B8" t="n">
-        <v>57400</v>
+        <v>57384</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1328,16 +1328,16 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1352,10 +1352,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>483129</v>
+        <v>483013</v>
       </c>
       <c r="R8" t="n">
-        <v>6989526</v>
+        <v>6989190</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1392,7 +1392,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>hack</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1419,7 +1419,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122386311</v>
+        <v>122386313</v>
       </c>
       <c r="B9" t="n">
         <v>57384</v>
@@ -1459,10 +1459,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>483013</v>
+        <v>483001</v>
       </c>
       <c r="R9" t="n">
-        <v>6989190</v>
+        <v>6989219</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1499,7 +1499,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1526,10 +1526,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122386313</v>
+        <v>122386323</v>
       </c>
       <c r="B10" t="n">
-        <v>57384</v>
+        <v>57400</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1542,16 +1542,16 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1566,10 +1566,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>483001</v>
+        <v>483129</v>
       </c>
       <c r="R10" t="n">
-        <v>6989219</v>
+        <v>6989526</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1606,7 +1606,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>ringhack</t>
+          <t>hack</t>
         </is>
       </c>
       <c r="AD10" t="b">

--- a/artfynd/A 60580-2024 artfynd.xlsx
+++ b/artfynd/A 60580-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY16"/>
+  <dimension ref="A1:AY15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122386320</v>
+        <v>122386324</v>
       </c>
       <c r="B2" t="n">
-        <v>57384</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>482875</v>
+        <v>483051</v>
       </c>
       <c r="R2" t="n">
-        <v>6989223</v>
+        <v>6989494</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -751,11 +746,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-01-30</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,32 +772,27 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122386321</v>
+        <v>122386323</v>
       </c>
       <c r="B3" t="n">
-        <v>57384</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -822,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>482832</v>
+        <v>483129</v>
       </c>
       <c r="R3" t="n">
-        <v>6989152</v>
+        <v>6989526</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -862,7 +847,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>ringhack färska</t>
+          <t>hack</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,15 +874,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122386319</v>
+        <v>122386310</v>
       </c>
       <c r="B4" t="n">
-        <v>57384</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -929,10 +909,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>482918</v>
+        <v>483003</v>
       </c>
       <c r="R4" t="n">
-        <v>6989264</v>
+        <v>6989199</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -996,15 +976,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122386324</v>
+        <v>122386311</v>
       </c>
       <c r="B5" t="n">
-        <v>79741</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1012,21 +987,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1036,10 +1011,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>483051</v>
+        <v>483013</v>
       </c>
       <c r="R5" t="n">
-        <v>6989494</v>
+        <v>6989190</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1072,6 +1047,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-01-30</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1098,15 +1078,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122386310</v>
+        <v>122386313</v>
       </c>
       <c r="B6" t="n">
-        <v>57384</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1138,10 +1113,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>483003</v>
+        <v>483001</v>
       </c>
       <c r="R6" t="n">
-        <v>6989199</v>
+        <v>6989219</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1178,7 +1153,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1205,15 +1180,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122386317</v>
+        <v>122386314</v>
       </c>
       <c r="B7" t="n">
-        <v>57384</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1239,16 +1209,28 @@
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Låshålet, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>483013</v>
+        <v>482998</v>
       </c>
       <c r="R7" t="n">
-        <v>6989410</v>
+        <v>6989231</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1281,11 +1263,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-01-30</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1312,15 +1289,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122386311</v>
+        <v>122386315</v>
       </c>
       <c r="B8" t="n">
-        <v>57384</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1345,17 +1317,33 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr"/>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Låshålet, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>483013</v>
+        <v>483057</v>
       </c>
       <c r="R8" t="n">
-        <v>6989190</v>
+        <v>6989286</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1388,11 +1376,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-01-30</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1419,15 +1402,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122386313</v>
+        <v>122386316</v>
       </c>
       <c r="B9" t="n">
-        <v>57384</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1459,10 +1437,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>483001</v>
+        <v>483242</v>
       </c>
       <c r="R9" t="n">
-        <v>6989219</v>
+        <v>6989315</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1499,7 +1477,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>ringhack</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1526,15 +1504,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122386323</v>
+        <v>122386317</v>
       </c>
       <c r="B10" t="n">
-        <v>57400</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1542,16 +1515,16 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1566,10 +1539,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>483129</v>
+        <v>483013</v>
       </c>
       <c r="R10" t="n">
-        <v>6989526</v>
+        <v>6989410</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1606,7 +1579,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>hack</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1633,15 +1606,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122386316</v>
+        <v>122386318</v>
       </c>
       <c r="B11" t="n">
-        <v>57384</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1673,10 +1641,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>483242</v>
+        <v>482996</v>
       </c>
       <c r="R11" t="n">
-        <v>6989315</v>
+        <v>6989426</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1740,15 +1708,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122386322</v>
+        <v>122386319</v>
       </c>
       <c r="B12" t="n">
-        <v>57384</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1780,10 +1743,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>482807</v>
+        <v>482918</v>
       </c>
       <c r="R12" t="n">
-        <v>6989125</v>
+        <v>6989264</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1820,7 +1783,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>ringhack färska</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1847,15 +1810,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122386318</v>
+        <v>122386320</v>
       </c>
       <c r="B13" t="n">
-        <v>57384</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1887,10 +1845,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>482996</v>
+        <v>482875</v>
       </c>
       <c r="R13" t="n">
-        <v>6989426</v>
+        <v>6989223</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1927,7 +1885,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1954,15 +1912,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122386315</v>
+        <v>122386321</v>
       </c>
       <c r="B14" t="n">
-        <v>57384</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1987,33 +1940,17 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Låshålet, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>483057</v>
+        <v>482832</v>
       </c>
       <c r="R14" t="n">
-        <v>6989286</v>
+        <v>6989152</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2046,6 +1983,11 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-01-30</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>ringhack färska</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2072,15 +2014,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122386314</v>
+        <v>122386322</v>
       </c>
       <c r="B15" t="n">
-        <v>57384</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2106,28 +2043,16 @@
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Låshålet, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>482998</v>
+        <v>482807</v>
       </c>
       <c r="R15" t="n">
-        <v>6989231</v>
+        <v>6989125</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2162,6 +2087,11 @@
           <t>2025-01-30</t>
         </is>
       </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>ringhack färska</t>
+        </is>
+      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
@@ -2183,108 +2113,6 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
-    </row>
-    <row r="16">
-      <c r="A16" t="n">
-        <v>122386328</v>
-      </c>
-      <c r="B16" t="n">
-        <v>90855</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E16" t="n">
-        <v>5432</v>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>Granticka</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>Porodaedalea chrysoloma</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
-      <c r="P16" t="inlineStr">
-        <is>
-          <t>Låshålet, Jmt</t>
-        </is>
-      </c>
-      <c r="Q16" t="n">
-        <v>483144</v>
-      </c>
-      <c r="R16" t="n">
-        <v>6989488</v>
-      </c>
-      <c r="S16" t="n">
-        <v>10</v>
-      </c>
-      <c r="T16" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U16" t="inlineStr">
-        <is>
-          <t>Östersund</t>
-        </is>
-      </c>
-      <c r="V16" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W16" t="inlineStr">
-        <is>
-          <t>Näs</t>
-        </is>
-      </c>
-      <c r="Y16" t="inlineStr">
-        <is>
-          <t>2025-01-30</t>
-        </is>
-      </c>
-      <c r="AA16" t="inlineStr">
-        <is>
-          <t>2025-01-30</t>
-        </is>
-      </c>
-      <c r="AD16" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE16" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG16" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT16" t="inlineStr"/>
-      <c r="AW16" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AX16" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY16" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 60580-2024 artfynd.xlsx
+++ b/artfynd/A 60580-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY15"/>
+  <dimension ref="A1:AZ15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122386324</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -871,6 +881,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122386323</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -973,6 +988,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122386310</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1075,6 +1095,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122386311</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1177,6 +1202,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122386313</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1286,6 +1316,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122386314</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1399,6 +1434,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122386315</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1501,6 +1541,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122386316</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1603,6 +1648,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122386317</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1705,6 +1755,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122386318</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1807,6 +1862,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122386319</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1909,6 +1969,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122386320</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2011,6 +2076,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122386321</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2113,8 +2183,29 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122386322</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>